--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Hobby.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Hobby.xlsx
@@ -518,11 +518,6 @@
           <t>土いじり</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Cuidar de plantas, flores ou hortas, mexendo com a terra.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -550,11 +545,6 @@
           <t>読書</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Mergulhar em livros, revistas ou qualquer material escrito.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -582,11 +572,6 @@
           <t>狩り</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Perseguir e capturar animais, geralmente por esporte ou sobrevivência.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -614,11 +599,6 @@
           <t>運動</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Praticar atividades físicas para manter a saúde e o corpo em forma.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -633,7 +613,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Instrumento Musical</t>
+          <t>Instrumento</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -644,11 +624,6 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>演奏</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Tocar violão, piano, bateria ou qualquer instrumento.</t>
         </is>
       </c>
     </row>
@@ -678,11 +653,6 @@
           <t>料理</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Preparar alimentos, explorar receitas e criar pratos saborosos.</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -710,11 +680,6 @@
           <t>お祈り</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Prática espiritual de se conectar com divindades ou forças superiores.</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -742,11 +707,6 @@
           <t>執筆</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Criar textos, histórias ou anotações com criatividade ou propósito.</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -774,11 +734,6 @@
           <t>絵描き</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Usar pincéis, tintas e criatividade para criar arte visual.</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -806,11 +761,6 @@
           <t>散歩</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Andar por lazer, saúde ou inspiração em ambientes variados.</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -838,11 +788,6 @@
           <t>風呂</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Relaxar e limpar o corpo com água quente ou fria.</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -857,7 +802,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Faxina</t>
+          <t>Limpeza</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -872,7 +817,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Limpar a casa</t>
+          <t>Limpar o lar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -912,11 +857,6 @@
           <t>歌唱</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Usar a voz para cantar músicas, sozinho ou com outros.</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -944,11 +884,6 @@
           <t>宝くじ</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Tentar a sorte em jogos de azar, esperando grandes prêmios.</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -976,11 +911,6 @@
           <t>ガチャ</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Participar de sistemas de sorteio (muito comum em jogos mobile).</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1008,11 +938,6 @@
           <t>日記</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Escrever pensamentos, sentimentos e eventos do dia a dia.</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1040,11 +965,6 @@
           <t>歴史</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Estudar ou se interessar por fatos e eventos do passado.</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1072,11 +992,6 @@
           <t>ブログ</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Criar conteúdo escrito online sobre assuntos de interesse pessoal.</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1091,7 +1006,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dormir</t>
+          <t>Sono</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1102,11 +1017,6 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>昼寝</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Tirar cochilos ou longos períodos de descanso para recuperar energia.</t>
         </is>
       </c>
     </row>
@@ -1136,11 +1046,6 @@
           <t>応援</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Apoiar com entusiasmo algo ou alguém, como em esportes.</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1168,11 +1073,6 @@
           <t>恋愛</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Interesse e envolvimento com sentimentos amorosos.</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1200,11 +1100,6 @@
           <t>自傷</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Prática autodestrutiva de causar dor a si mesmo.</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1232,11 +1127,6 @@
           <t>薬</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Uso de substâncias que alteram o estado mental ou físico.</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1251,7 +1141,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lavagem de Roupa</t>
+          <t>Lavagem</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1262,11 +1152,6 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>洗濯</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Atividade de limpar roupas sujas.</t>
         </is>
       </c>
     </row>
@@ -1296,11 +1181,6 @@
           <t>ゴミ漁り</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Vasculhar lixo ou restos em busca de algo útil ou valioso.</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1328,11 +1208,6 @@
           <t>ダイエット</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Manter controle alimentar para saúde, estética ou objetivos pessoais.</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1360,11 +1235,6 @@
           <t>手芸</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Criar objetos manuais como bordados, esculturas ou bijuterias.</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1392,11 +1262,6 @@
           <t>ショッピング</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Atividade de adquirir produtos por necessidade ou prazer.</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1411,7 +1276,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Beber</t>
+          <t>Bebida</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1422,11 +1287,6 @@
       <c r="E31" t="inlineStr">
         <is>
           <t>飲酒</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Ingerir bebidas alcoólicas social ou recreativamente.</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1303,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fumar</t>
+          <t>Fumo</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1485,7 +1345,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cuidar de Alguém</t>
+          <t>Cuidado</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1527,7 +1387,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jogar</t>
+          <t>Jogo</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1538,11 +1398,6 @@
       <c r="E34" t="inlineStr">
         <is>
           <t>ゲーム</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Praticar jogos eletrônicos, de tabuleiro ou físicos por diversão.</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1414,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Acariciar Coisas Fofas</t>
+          <t>Carinho Fofinho</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1570,11 +1425,6 @@
       <c r="E35" t="inlineStr">
         <is>
           <t>モフモフ</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Tocar e acariciar animais ou objetos macios.</t>
         </is>
       </c>
     </row>
@@ -1604,11 +1454,6 @@
           <t>気持ちいいこと</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Atividades íntimas de autossatisfação.</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1623,7 +1468,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bicho de Estimação</t>
+          <t>Bicho</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1634,11 +1479,6 @@
       <c r="E37" t="inlineStr">
         <is>
           <t>ペット</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Cuidar de animais como cães, gatos, pássaros, etc.</t>
         </is>
       </c>
     </row>
@@ -1668,11 +1508,6 @@
           <t>瞑想</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Focar na respiração e mente para relaxamento e clareza mental.</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1700,11 +1535,6 @@
           <t>骨董品</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Interesse por objetos e itens antigos, colecionáveis.</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1719,7 +1549,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Fazenda</t>
+          <t>Agricultura</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1730,11 +1560,6 @@
       <c r="E40" t="inlineStr">
         <is>
           <t>農作業</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Cultivar plantações ou cuidar de animais em ambiente rural.</t>
         </is>
       </c>
     </row>
@@ -1806,11 +1631,6 @@
           <t>研究</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Investigar assuntos em busca de conhecimento ou soluções.</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1838,11 +1658,6 @@
           <t>釣り</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Atividade de capturar peixes com vara, rede ou anzol.</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1870,11 +1685,6 @@
           <t>探検</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Aventure-se por locais desconhecidos ou inexplorados.</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1889,7 +1699,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Afazeres Domésticos</t>
+          <t>Tarefas</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1904,7 +1714,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Limpar a casa</t>
+          <t>Limpar o lar</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1931,7 +1741,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ferreiro</t>
+          <t>Ferraria</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1942,11 +1752,6 @@
       <c r="E46" t="inlineStr">
         <is>
           <t>鍛冶</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Trabalhar com metais para criar armas, ferramentas ou objetos.</t>
         </is>
       </c>
     </row>
@@ -1976,11 +1781,6 @@
           <t>木こり</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Cortar árvores e lidar com madeira como recurso.</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1995,7 +1795,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Procriação(Animais)</t>
+          <t>Criação</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2006,11 +1806,6 @@
       <c r="E48" t="inlineStr">
         <is>
           <t>繁殖</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Criar e cuidar da reprodução de plantas ou animais.</t>
         </is>
       </c>
     </row>
@@ -2040,11 +1835,6 @@
           <t>監査</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Atuar como responsável ou líder de um grupo ou projeto.</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2072,11 +1862,6 @@
           <t>暗殺</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Eliminar alvos de forma furtiva ou violenta (em contexto fictício, claro).</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2091,12 +1876,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Esbanjamento</t>
+          <t>Extravagância</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extravagance </t>
+          <t>Extravagance</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2146,11 +1931,6 @@
           <t>ランボー</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Estilo de combate agressivo e solitário, estilo "um exército de um homem só".</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2165,7 +1945,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boatos</t>
+          <t>Fofoca</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2176,11 +1956,6 @@
       <c r="E53" t="inlineStr">
         <is>
           <t>噂話</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Espalhar ou escutar rumores, fofocas e histórias.</t>
         </is>
       </c>
     </row>
@@ -2212,7 +1987,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Coletar tesouros automaticamente (Requer mapa do tesouro)</t>
+          <t>Coleta automática de tesouros (Requer mapa do tesouro)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2239,7 +2014,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Acúmulo de Coisas</t>
+          <t>Acumulação</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2250,11 +2025,6 @@
       <c r="E55" t="inlineStr">
         <is>
           <t>財宝集め</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Guardar e colecionar itens, muitas vezes sem uso imediato.</t>
         </is>
       </c>
     </row>
